--- a/product_selector_out/STM32 wireless MCUs.xlsx
+++ b/product_selector_out/STM32 wireless MCUs.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="BP30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BP31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="BP33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="BP35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BP36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="BP37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="BP38" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="BP39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="BP40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="BP41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="BP43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="BP44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="BP46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="BP47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="BP48" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="BP49" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="BP50" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="BP52" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="BP53" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="BP54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="BP55" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="BP56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="BP57" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="BP58" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="BP59" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="BP60" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="BP61" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="BP62" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="BP64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="BP65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="BP66" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20160,7 +20160,7 @@
       </c>
       <c r="BP67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="BP68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="BP69" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="BP70" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="BP71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21870,7 +21870,7 @@
       </c>
       <c r="BP72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22212,7 +22212,7 @@
       </c>
       <c r="BP73" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="BP74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       </c>
       <c r="BP77" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="BP78" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="BP79" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25974,7 +25974,7 @@
       </c>
       <c r="BP84" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26658,7 +26658,7 @@
       </c>
       <c r="BP86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="BP87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27342,7 +27342,7 @@
       </c>
       <c r="BP88" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27684,7 +27684,7 @@
       </c>
       <c r="BP89" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="BP91" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="BP92" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29052,7 +29052,7 @@
       </c>
       <c r="BP93" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29394,7 +29394,7 @@
       </c>
       <c r="BP94" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="BP95" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30078,7 +30078,7 @@
       </c>
       <c r="BP96" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="BP97" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -31788,7 +31788,7 @@
       </c>
       <c r="BP101" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32130,7 +32130,7 @@
       </c>
       <c r="BP102" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32472,7 +32472,7 @@
       </c>
       <c r="BP103" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="BP104" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -33498,7 +33498,7 @@
       </c>
       <c r="BP106" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -33525,7 +33525,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Arm Cortex-M0+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="BP107" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -34904,9 +34904,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -35219,9 +35219,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35246,9 +35246,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -35561,9 +35561,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35930,9 +35930,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -36245,9 +36245,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36272,9 +36272,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -36587,9 +36587,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36614,9 +36614,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -36929,9 +36929,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36956,9 +36956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -37271,9 +37271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37640,9 +37640,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -37955,9 +37955,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37982,9 +37982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -38297,9 +38297,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38324,9 +38324,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -38639,9 +38639,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39008,9 +39008,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -39323,9 +39323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39692,9 +39692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -39917,14 +39917,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -40007,9 +40007,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40034,9 +40034,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -40259,14 +40259,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -40349,9 +40349,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40376,9 +40376,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -40601,14 +40601,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -40691,9 +40691,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40718,9 +40718,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -40943,14 +40943,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -41033,9 +41033,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41060,9 +41060,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -41285,14 +41285,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -41375,9 +41375,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41402,9 +41402,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -41627,14 +41627,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -41717,9 +41717,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41744,9 +41744,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -41969,14 +41969,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -42059,9 +42059,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42428,9 +42428,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -42653,14 +42653,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -42743,9 +42743,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42770,9 +42770,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -42995,14 +42995,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -43085,9 +43085,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43112,9 +43112,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -43337,14 +43337,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -43427,9 +43427,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43454,9 +43454,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -43679,14 +43679,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ38" s="6" t="inlineStr">
@@ -43769,9 +43769,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43796,9 +43796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -44021,14 +44021,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ39" s="6" t="inlineStr">
@@ -44111,9 +44111,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44138,9 +44138,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -44363,14 +44363,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -44453,9 +44453,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44480,9 +44480,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -44705,14 +44705,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ41" s="6" t="inlineStr">
@@ -44795,9 +44795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45164,9 +45164,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -45389,14 +45389,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ43" s="8" t="inlineStr">
@@ -45479,9 +45479,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45506,9 +45506,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -45731,14 +45731,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ44" s="8" t="inlineStr">
@@ -45821,9 +45821,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46190,9 +46190,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -46415,14 +46415,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ46" s="8" t="inlineStr">
@@ -46505,9 +46505,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46532,9 +46532,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -46757,14 +46757,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ47" s="8" t="inlineStr">
@@ -46847,9 +46847,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46874,9 +46874,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -47099,14 +47099,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ48" s="8" t="inlineStr">
@@ -47189,9 +47189,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47216,9 +47216,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -47441,14 +47441,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX49" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ49" s="8" t="inlineStr">
@@ -47531,9 +47531,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47558,9 +47558,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -47783,14 +47783,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ50" s="8" t="inlineStr">
@@ -47873,9 +47873,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48242,9 +48242,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -48467,14 +48467,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ52" s="8" t="inlineStr">
@@ -48557,9 +48557,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48584,9 +48584,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -48809,14 +48809,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ53" s="8" t="inlineStr">
@@ -48899,9 +48899,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48926,9 +48926,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -49151,14 +49151,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ54" s="8" t="inlineStr">
@@ -49241,9 +49241,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49268,9 +49268,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -49493,14 +49493,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX55" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ55" s="8" t="inlineStr">
@@ -49583,9 +49583,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49610,9 +49610,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -49835,14 +49835,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ56" s="8" t="inlineStr">
@@ -49925,9 +49925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49952,9 +49952,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -50017,14 +50017,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
@@ -50177,14 +50177,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ57" s="8" t="inlineStr">
@@ -50267,9 +50267,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50294,9 +50294,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -50359,14 +50359,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
@@ -50519,14 +50519,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ58" s="8" t="inlineStr">
@@ -50609,9 +50609,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50636,9 +50636,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -50701,14 +50701,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T59" s="6" t="inlineStr">
@@ -50861,14 +50861,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ59" s="8" t="inlineStr">
@@ -50951,9 +50951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50978,9 +50978,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -51043,14 +51043,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
@@ -51203,14 +51203,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ60" s="8" t="inlineStr">
@@ -51293,9 +51293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51320,9 +51320,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -51385,14 +51385,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -51545,14 +51545,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ61" s="8" t="inlineStr">
@@ -51635,9 +51635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51662,9 +51662,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -51727,14 +51727,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -51887,14 +51887,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ62" s="8" t="inlineStr">
@@ -51977,9 +51977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52234,9 +52234,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AY63" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AY63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ63" s="8" t="inlineStr">
@@ -52346,9 +52346,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -52411,14 +52411,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
@@ -52571,14 +52571,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ64" s="8" t="inlineStr">
@@ -52661,9 +52661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52688,9 +52688,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -52753,14 +52753,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -52913,14 +52913,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ65" s="8" t="inlineStr">
@@ -53003,9 +53003,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53030,9 +53030,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -53095,14 +53095,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T66" s="6" t="inlineStr">
@@ -53255,14 +53255,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ66" s="8" t="inlineStr">
@@ -53345,9 +53345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53372,9 +53372,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -53437,14 +53437,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -53597,14 +53597,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ67" s="8" t="inlineStr">
@@ -53687,9 +53687,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53714,9 +53714,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -53779,14 +53779,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -53939,14 +53939,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ68" s="8" t="inlineStr">
@@ -54029,9 +54029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54056,9 +54056,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -54121,14 +54121,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
@@ -54281,14 +54281,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ69" s="8" t="inlineStr">
@@ -54371,9 +54371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54398,9 +54398,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -54463,14 +54463,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
@@ -54623,14 +54623,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ70" s="8" t="inlineStr">
@@ -54713,9 +54713,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54740,9 +54740,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -54805,14 +54805,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -54965,14 +54965,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ71" s="8" t="inlineStr">
@@ -55055,9 +55055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55082,9 +55082,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -55147,14 +55147,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -55307,14 +55307,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ72" s="8" t="inlineStr">
@@ -55397,9 +55397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55424,9 +55424,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -55489,14 +55489,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T73" s="6" t="inlineStr">
@@ -55649,14 +55649,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ73" s="8" t="inlineStr">
@@ -55739,9 +55739,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55766,9 +55766,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -55831,14 +55831,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -55991,14 +55991,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ74" s="8" t="inlineStr">
@@ -56081,9 +56081,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56792,9 +56792,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -57017,14 +57017,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX77" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ77" s="6" t="inlineStr">
@@ -57107,9 +57107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57134,9 +57134,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -57359,14 +57359,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX78" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ78" s="6" t="inlineStr">
@@ -57449,9 +57449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57476,9 +57476,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -57701,14 +57701,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX79" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ79" s="6" t="inlineStr">
@@ -57791,9 +57791,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -59186,9 +59186,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -59411,14 +59411,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ84" s="6" t="inlineStr">
@@ -59501,9 +59501,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -59865,14 +59865,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -59990,9 +59990,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD86" s="6" t="inlineStr">
@@ -60035,9 +60035,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM86" s="6" t="inlineStr">
@@ -60095,14 +60095,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ86" s="6" t="inlineStr">
@@ -60185,9 +60185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -60207,14 +60207,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -60332,9 +60332,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD87" s="6" t="inlineStr">
@@ -60377,9 +60377,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM87" s="6" t="inlineStr">
@@ -60437,14 +60437,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ87" s="6" t="inlineStr">
@@ -60527,9 +60527,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -60549,14 +60549,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -60674,9 +60674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD88" s="6" t="inlineStr">
@@ -60719,9 +60719,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM88" s="6" t="inlineStr">
@@ -60779,14 +60779,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX88" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ88" s="6" t="inlineStr">
@@ -60869,9 +60869,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -60891,14 +60891,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -61016,9 +61016,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD89" s="6" t="inlineStr">
@@ -61061,9 +61061,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM89" s="6" t="inlineStr">
@@ -61121,14 +61121,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX89" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ89" s="6" t="inlineStr">
@@ -61211,9 +61211,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -61575,14 +61575,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -61700,9 +61700,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD91" s="6" t="inlineStr">
@@ -61745,9 +61745,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM91" s="6" t="inlineStr">
@@ -61805,14 +61805,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX91" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ91" s="6" t="inlineStr">
@@ -61895,9 +61895,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -61917,14 +61917,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -62042,9 +62042,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD92" s="6" t="inlineStr">
@@ -62087,9 +62087,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM92" s="6" t="inlineStr">
@@ -62147,14 +62147,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ92" s="6" t="inlineStr">
@@ -62237,9 +62237,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62259,14 +62259,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -62384,9 +62384,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD93" s="6" t="inlineStr">
@@ -62429,9 +62429,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM93" s="6" t="inlineStr">
@@ -62489,14 +62489,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX93" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ93" s="6" t="inlineStr">
@@ -62579,9 +62579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62601,14 +62601,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -62726,9 +62726,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD94" s="6" t="inlineStr">
@@ -62771,9 +62771,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM94" s="6" t="inlineStr">
@@ -62831,14 +62831,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX94" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ94" s="6" t="inlineStr">
@@ -62921,9 +62921,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62943,14 +62943,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -63068,9 +63068,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD95" s="8" t="inlineStr">
@@ -63113,9 +63113,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM95" s="6" t="inlineStr">
@@ -63173,14 +63173,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX95" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ95" s="6" t="inlineStr">
@@ -63263,9 +63263,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -63285,14 +63285,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -63410,9 +63410,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD96" s="8" t="inlineStr">
@@ -63455,9 +63455,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM96" s="6" t="inlineStr">
@@ -63515,14 +63515,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX96" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ96" s="6" t="inlineStr">
@@ -63605,9 +63605,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -63627,14 +63627,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -63752,9 +63752,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD97" s="6" t="inlineStr">
@@ -63797,9 +63797,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM97" s="6" t="inlineStr">
@@ -63857,14 +63857,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ97" s="6" t="inlineStr">
@@ -63947,9 +63947,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -65315,9 +65315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP101" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -65657,9 +65657,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP102" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -65919,9 +65919,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AZ103" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AZ103" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA103" s="6" t="inlineStr">
@@ -65999,9 +65999,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP103" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -66341,9 +66341,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP104" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP104" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -67025,9 +67025,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP106" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -67052,9 +67052,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -67367,9 +67367,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP107" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -67388,7 +67388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67444,7 +67444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -67466,7 +67466,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -67481,14 +67481,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WLE4C8</t>
+          <t>STM32WLE5C8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -67503,14 +67503,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32WLE5JB</t>
+          <t>STM32WBA50KG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -67525,19 +67525,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32WL54JC</t>
+          <t>STM32WBA52CE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -67547,19 +67547,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32WL54JC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -67569,19 +67569,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32WLE5CC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -67591,14 +67591,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32WLE5JC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -67613,19 +67613,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32WL55JC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -67635,14 +67635,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32WL55JC</t>
+          <t>STM32WBA25CE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -67657,14 +67657,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WB1MMC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -67679,19 +67679,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WB5MMG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -67701,14 +67701,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32WLE5J8</t>
+          <t>STM32WB10CC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -67723,14 +67723,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32WLE4J8</t>
+          <t>STM32WB50CG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -67745,14 +67745,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32WLE4JB</t>
+          <t>STM32WB15CC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -67767,19 +67767,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32WLE4CB</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -67789,14 +67789,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32WLE4CC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -67811,19 +67811,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32WLE4JC</t>
+          <t>STM32WB05KZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -67832,2338 +67832,6 @@
         </is>
       </c>
       <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WLE5CB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WLE5C8</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WBA52KE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WBA55UE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WBA50KG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WBA52KG</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32WBA54KG</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32WBA52CG</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32WBA55UG</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32WBA55CE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32WBA52CE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32WBA54KE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32WBA54CE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32WBA55HG</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32WBA54CG</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32WBA55CG</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32WBA25CE</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32WBA23KE</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32WBA25HE</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32WBA23CE</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32WB1MMC</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32WB5MMG</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32WB10CC</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32WB50CG</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32WB30CE</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32WB15CC</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32WB55RC</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32WB55RC</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32WB05KZ</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32WB05TZ</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
         <is>
           <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
         </is>

--- a/product_selector_out/STM32 wireless MCUs.xlsx
+++ b/product_selector_out/STM32 wireless MCUs.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="BP30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BP31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="BP33" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="BP35" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="BP36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="BP37" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="BP38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="BP39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="BP40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="BP41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="BP43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="BP44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="BP46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="BP47" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="BP48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="BP49" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="BP50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -15030,7 +15030,7 @@
       </c>
       <c r="BP52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="BP53" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="BP54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="BP55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="BP56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="BP57" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="BP58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="BP59" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -17766,7 +17766,7 @@
       </c>
       <c r="BP60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="BP61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="BP62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="BP64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="BP65" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="BP66" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -20160,7 +20160,7 @@
       </c>
       <c r="BP67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="BP68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="BP69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="BP70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="BP71" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -21870,7 +21870,7 @@
       </c>
       <c r="BP72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -22212,7 +22212,7 @@
       </c>
       <c r="BP73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="BP74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       </c>
       <c r="BP77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="BP78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
     </row>
@@ -24264,7 +24264,7 @@
       </c>
       <c r="BP79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
     </row>
@@ -25974,7 +25974,7 @@
       </c>
       <c r="BP84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
         </is>
       </c>
     </row>
@@ -26658,7 +26658,7 @@
       </c>
       <c r="BP86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="BP87" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -27342,7 +27342,7 @@
       </c>
       <c r="BP88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -27684,7 +27684,7 @@
       </c>
       <c r="BP89" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="BP91" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -28710,7 +28710,7 @@
       </c>
       <c r="BP92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -29052,7 +29052,7 @@
       </c>
       <c r="BP93" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -29394,7 +29394,7 @@
       </c>
       <c r="BP94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="BP95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -30078,7 +30078,7 @@
       </c>
       <c r="BP96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="BP97" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -31788,7 +31788,7 @@
       </c>
       <c r="BP101" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
     </row>
@@ -32130,7 +32130,7 @@
       </c>
       <c r="BP102" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
     </row>
@@ -32472,7 +32472,7 @@
       </c>
       <c r="BP103" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="BP104" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
     </row>
@@ -33498,7 +33498,7 @@
       </c>
       <c r="BP106" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
         </is>
       </c>
     </row>
@@ -33525,7 +33525,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Arm Cortex-M0+</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="BP107" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
         </is>
       </c>
     </row>
@@ -34904,9 +34904,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -35219,9 +35219,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35246,9 +35246,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -35561,9 +35561,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -35930,9 +35930,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -36245,9 +36245,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36272,9 +36272,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -36587,9 +36587,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36614,9 +36614,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -36929,9 +36929,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36956,9 +36956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -37271,9 +37271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -37640,9 +37640,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -37955,9 +37955,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -37982,9 +37982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -38297,9 +38297,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -38324,9 +38324,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -38639,9 +38639,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -39008,9 +39008,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -39323,9 +39323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -39692,9 +39692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -39917,14 +39917,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -40007,9 +40007,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -40034,9 +40034,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -40259,14 +40259,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -40349,9 +40349,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -40376,9 +40376,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -40601,14 +40601,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -40691,9 +40691,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -40718,9 +40718,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -40943,14 +40943,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -41033,9 +41033,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41060,9 +41060,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -41285,14 +41285,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -41375,9 +41375,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41402,9 +41402,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -41627,14 +41627,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -41717,9 +41717,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41744,9 +41744,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -41969,14 +41969,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -42059,9 +42059,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42428,9 +42428,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -42653,14 +42653,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -42743,9 +42743,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -42770,9 +42770,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -42995,14 +42995,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -43085,9 +43085,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -43112,9 +43112,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -43337,14 +43337,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -43427,9 +43427,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -43454,9 +43454,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -43679,14 +43679,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ38" s="6" t="inlineStr">
@@ -43769,9 +43769,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -43796,9 +43796,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -44021,14 +44021,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ39" s="6" t="inlineStr">
@@ -44111,9 +44111,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44138,9 +44138,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -44363,14 +44363,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -44453,9 +44453,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44480,9 +44480,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -44705,14 +44705,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ41" s="6" t="inlineStr">
@@ -44795,9 +44795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45164,9 +45164,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -45389,14 +45389,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ43" s="8" t="inlineStr">
@@ -45479,9 +45479,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45506,9 +45506,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -45731,14 +45731,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ44" s="8" t="inlineStr">
@@ -45821,9 +45821,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46190,9 +46190,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -46415,14 +46415,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ46" s="8" t="inlineStr">
@@ -46505,9 +46505,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46532,9 +46532,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -46757,14 +46757,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ47" s="8" t="inlineStr">
@@ -46847,9 +46847,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46874,9 +46874,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -47099,14 +47099,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ48" s="8" t="inlineStr">
@@ -47189,9 +47189,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -47216,9 +47216,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -47441,14 +47441,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ49" s="8" t="inlineStr">
@@ -47531,9 +47531,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP49" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -47558,9 +47558,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -47783,14 +47783,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY50" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ50" s="8" t="inlineStr">
@@ -47873,9 +47873,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -48242,9 +48242,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -48467,14 +48467,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY52" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ52" s="8" t="inlineStr">
@@ -48557,9 +48557,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP52" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -48584,9 +48584,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -48809,14 +48809,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ53" s="8" t="inlineStr">
@@ -48899,9 +48899,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP53" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -48926,9 +48926,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -49151,14 +49151,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ54" s="8" t="inlineStr">
@@ -49241,9 +49241,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP54" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49268,9 +49268,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -49493,14 +49493,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY55" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ55" s="8" t="inlineStr">
@@ -49583,9 +49583,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP55" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49610,9 +49610,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -49835,14 +49835,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ56" s="8" t="inlineStr">
@@ -49925,9 +49925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP56" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49952,9 +49952,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -50017,14 +50017,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
@@ -50177,14 +50177,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ57" s="8" t="inlineStr">
@@ -50267,9 +50267,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP57" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50294,9 +50294,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -50359,14 +50359,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
@@ -50519,14 +50519,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ58" s="8" t="inlineStr">
@@ -50609,9 +50609,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP58" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50636,9 +50636,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -50701,14 +50701,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T59" s="6" t="inlineStr">
@@ -50861,14 +50861,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ59" s="8" t="inlineStr">
@@ -50951,9 +50951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP59" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50978,9 +50978,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -51043,14 +51043,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R60" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S60" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="R60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
@@ -51203,14 +51203,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ60" s="8" t="inlineStr">
@@ -51293,9 +51293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP60" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51320,9 +51320,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -51385,14 +51385,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -51545,14 +51545,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ61" s="8" t="inlineStr">
@@ -51635,9 +51635,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP61" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51662,9 +51662,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -51727,14 +51727,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -51887,14 +51887,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ62" s="8" t="inlineStr">
@@ -51977,9 +51977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52346,9 +52346,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -52411,14 +52411,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="R64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
@@ -52571,14 +52571,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ64" s="8" t="inlineStr">
@@ -52661,9 +52661,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52688,9 +52688,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -52753,14 +52753,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -52913,14 +52913,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ65" s="8" t="inlineStr">
@@ -53003,9 +53003,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -53030,9 +53030,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -53095,14 +53095,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R66" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S66" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="R66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T66" s="6" t="inlineStr">
@@ -53255,14 +53255,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ66" s="8" t="inlineStr">
@@ -53345,9 +53345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP66" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -53372,9 +53372,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -53437,14 +53437,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -53597,14 +53597,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ67" s="8" t="inlineStr">
@@ -53687,9 +53687,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -53714,9 +53714,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -53779,14 +53779,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -53939,14 +53939,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ68" s="8" t="inlineStr">
@@ -54029,9 +54029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54056,9 +54056,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -54121,14 +54121,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
@@ -54281,14 +54281,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ69" s="8" t="inlineStr">
@@ -54371,9 +54371,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP69" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54398,9 +54398,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -54463,14 +54463,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="R70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
@@ -54623,14 +54623,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ70" s="8" t="inlineStr">
@@ -54713,9 +54713,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54740,9 +54740,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -54805,14 +54805,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -54965,14 +54965,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ71" s="8" t="inlineStr">
@@ -55055,9 +55055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55082,9 +55082,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -55147,14 +55147,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -55307,14 +55307,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ72" s="8" t="inlineStr">
@@ -55397,9 +55397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55424,9 +55424,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -55489,14 +55489,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T73" s="6" t="inlineStr">
@@ -55649,14 +55649,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ73" s="8" t="inlineStr">
@@ -55739,9 +55739,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP73" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55766,9 +55766,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -55831,14 +55831,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="S74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="R74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -55991,14 +55991,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ74" s="8" t="inlineStr">
@@ -56081,9 +56081,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -56792,9 +56792,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -57017,14 +57017,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY77" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ77" s="6" t="inlineStr">
@@ -57107,9 +57107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP77" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57134,9 +57134,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -57359,14 +57359,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY78" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ78" s="6" t="inlineStr">
@@ -57449,9 +57449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP78" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -57476,9 +57476,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -57701,14 +57701,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ79" s="6" t="inlineStr">
@@ -57791,9 +57791,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP79" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -59186,9 +59186,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -59411,14 +59411,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ84" s="6" t="inlineStr">
@@ -59501,9 +59501,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP84" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -59865,14 +59865,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -59990,9 +59990,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD86" s="6" t="inlineStr">
@@ -60035,9 +60035,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM86" s="6" t="inlineStr">
@@ -60095,14 +60095,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ86" s="6" t="inlineStr">
@@ -60185,9 +60185,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -60207,14 +60207,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -60332,9 +60332,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD87" s="6" t="inlineStr">
@@ -60377,9 +60377,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM87" s="6" t="inlineStr">
@@ -60437,14 +60437,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ87" s="6" t="inlineStr">
@@ -60527,9 +60527,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP87" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -60549,14 +60549,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -60674,9 +60674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC88" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD88" s="6" t="inlineStr">
@@ -60719,9 +60719,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL88" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM88" s="6" t="inlineStr">
@@ -60779,14 +60779,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY88" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ88" s="6" t="inlineStr">
@@ -60869,9 +60869,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP88" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -60891,14 +60891,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -61016,9 +61016,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD89" s="6" t="inlineStr">
@@ -61061,9 +61061,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM89" s="6" t="inlineStr">
@@ -61121,14 +61121,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ89" s="6" t="inlineStr">
@@ -61211,9 +61211,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP89" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -61575,14 +61575,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -61700,9 +61700,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD91" s="6" t="inlineStr">
@@ -61745,9 +61745,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM91" s="6" t="inlineStr">
@@ -61805,14 +61805,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ91" s="6" t="inlineStr">
@@ -61895,9 +61895,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP91" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -61917,14 +61917,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -62042,9 +62042,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD92" s="6" t="inlineStr">
@@ -62087,9 +62087,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM92" s="6" t="inlineStr">
@@ -62147,14 +62147,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ92" s="6" t="inlineStr">
@@ -62237,9 +62237,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP92" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -62259,14 +62259,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -62384,9 +62384,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC93" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD93" s="6" t="inlineStr">
@@ -62429,9 +62429,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL93" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM93" s="6" t="inlineStr">
@@ -62489,14 +62489,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY93" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ93" s="6" t="inlineStr">
@@ -62579,9 +62579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP93" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -62601,14 +62601,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -62726,9 +62726,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC94" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD94" s="6" t="inlineStr">
@@ -62771,9 +62771,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL94" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM94" s="6" t="inlineStr">
@@ -62831,14 +62831,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY94" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ94" s="6" t="inlineStr">
@@ -62921,9 +62921,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP94" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -62943,14 +62943,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -63068,9 +63068,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC95" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD95" s="8" t="inlineStr">
@@ -63113,9 +63113,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL95" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM95" s="6" t="inlineStr">
@@ -63173,14 +63173,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY95" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ95" s="6" t="inlineStr">
@@ -63263,9 +63263,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP95" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -63285,14 +63285,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -63410,9 +63410,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC96" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD96" s="8" t="inlineStr">
@@ -63455,9 +63455,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL96" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM96" s="6" t="inlineStr">
@@ -63515,14 +63515,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY96" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ96" s="6" t="inlineStr">
@@ -63605,9 +63605,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP96" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -63627,14 +63627,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -63752,9 +63752,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC97" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD97" s="6" t="inlineStr">
@@ -63797,9 +63797,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL97" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM97" s="6" t="inlineStr">
@@ -63857,14 +63857,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX97" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY97" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ97" s="6" t="inlineStr">
@@ -63947,9 +63947,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP97" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -65315,9 +65315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP101" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP101" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -65657,9 +65657,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP102" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP102" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -65919,9 +65919,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AZ103" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AZ103" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="BA103" s="6" t="inlineStr">
@@ -65999,9 +65999,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP103" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP103" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -66341,9 +66341,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP104" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP104" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -67025,9 +67025,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP106" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP106" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -67052,9 +67052,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -67367,9 +67367,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP107" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP107" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -67388,7 +67388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67444,7 +67444,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WL54CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -67466,7 +67466,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WL54CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -67488,7 +67488,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WLE5C8</t>
+          <t>STM32WLE4C8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -67510,7 +67510,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32WBA50KG</t>
+          <t>STM32WLE5JB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -67525,19 +67525,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32WBA52CE</t>
+          <t>STM32WL54JC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -67547,19 +67547,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WL54JC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -67569,19 +67569,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WLE5CC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -67591,14 +67591,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WLE5JC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -67613,19 +67613,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32WBA62CI</t>
+          <t>STM32WL55JC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) max</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -67635,14 +67635,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32WBA25CE</t>
+          <t>STM32WL55JC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -67657,14 +67657,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32WB1MMC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -67679,19 +67679,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32WB5MMG</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -67701,14 +67701,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32WB10CC</t>
+          <t>STM32WLE5J8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -67723,14 +67723,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32WB50CG</t>
+          <t>STM32WLE4J8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -67745,14 +67745,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32WB15CC</t>
+          <t>STM32WLE4JB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -67767,19 +67767,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WLE4CB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -67789,14 +67789,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WLE4CC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -67811,27 +67811,2755 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>STM32WLE4JC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32WLE5CB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32WLE5C8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32WBA52KE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32WBA55UE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32WBA50KG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32WBA52KG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32WBA54KG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32WBA52CG</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32WBA55UG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32WBA55CE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32WBA52CE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32WBA54KE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32WBA54CE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32WBA55HG</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32WBA54CG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32WBA55CG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32WBA62PI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32WBA62PI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32WBA62PI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32WBA62PI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32WBA65CI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32WBA65MI</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32WBA62MI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32WBA65PI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32WBA64CG</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32WBA62CI</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32WBA65CG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32WBA64CI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32WBA62MG</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32WBA65PG</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32WBA63CG</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32WBA62PG</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32WBA62CG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32WBA65RI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32WBA65RG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32WBA63CI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32WBA65MG</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32WBA25CE</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32WBA23KE</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32WBA25HE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32WBA23CE</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32WB1MMC</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32WB5MMG</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32WB10CC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32WB50CG</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32WB30CE</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32WB15CC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32WB55RC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32WB55RC</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32WB55VG</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32WB55VG</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32WB55VY</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32WB55VY</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32WB55VE</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32WB55VE</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32WB55CC</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32WB55CC</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32WB55RE</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32WB55RE</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32WB55VC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32WB55VC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32WB55CG</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32WB55CG</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32WB55RG</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32WB55RG</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>STM32WB05KZ</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32WB05TZ</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
         <is>
           <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
         </is>

--- a/product_selector_out/STM32 wireless MCUs.xlsx
+++ b/product_selector_out/STM32 wireless MCUs.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -27434,7 +27440,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S89" s="4" t="inlineStr">
@@ -28460,7 +28466,7 @@
       </c>
       <c r="R92" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S92" s="4" t="inlineStr">
@@ -59935,14 +59941,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R86" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T86" s="6" t="inlineStr">
@@ -60277,14 +60283,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R87" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T87" s="6" t="inlineStr">
@@ -60619,14 +60625,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R88" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T88" s="6" t="inlineStr">
@@ -60961,14 +60967,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R89" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S89" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T89" s="6" t="inlineStr">
@@ -61303,14 +61309,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R90" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T90" s="6" t="inlineStr">
@@ -61645,14 +61651,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R91" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T91" s="6" t="inlineStr">
@@ -61987,14 +61993,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R92" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S92" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T92" s="6" t="inlineStr">
@@ -62329,14 +62335,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R93" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S93" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T93" s="6" t="inlineStr">
@@ -62671,14 +62677,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R94" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S94" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T94" s="6" t="inlineStr">
@@ -63013,14 +63019,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R95" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S95" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T95" s="6" t="inlineStr">
@@ -63355,14 +63361,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R96" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S96" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T96" s="6" t="inlineStr">
@@ -63697,14 +63703,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R97" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S97" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T97" s="6" t="inlineStr">

--- a/product_selector_out/STM32 wireless MCUs.xlsx
+++ b/product_selector_out/STM32 wireless MCUs.xlsx
@@ -1698,7 +1698,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="BP28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="BP29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="BP30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="BP31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="BP32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="BP33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="BP35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="BP36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="BP37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP38" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="BP39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="BP40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="BP41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="BP43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="BP44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="BP46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="BP47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="BP48" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="BP49" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
       </c>
       <c r="BP50" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="BP52" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="BP53" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="BP54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="BP55" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="BP56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="BP57" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="BP58" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="BP59" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="BP60" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="BP61" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="BP62" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="BP64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19482,7 +19482,7 @@
       </c>
       <c r="BP65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="BP66" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
       </c>
       <c r="BP67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20508,7 @@
       </c>
       <c r="BP68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
       </c>
       <c r="BP69" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21192,7 +21192,7 @@
       </c>
       <c r="BP70" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="BP71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="BP72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="BP73" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="BP74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23586,7 +23586,7 @@
       </c>
       <c r="BP77" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="BP78" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24270,7 +24270,7 @@
       </c>
       <c r="BP79" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25980,7 +25980,7 @@
       </c>
       <c r="BP84" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26664,7 +26664,7 @@
       </c>
       <c r="BP86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27006,7 +27006,7 @@
       </c>
       <c r="BP87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="BP88" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27440,7 +27440,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="S89" s="4" t="inlineStr">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="BP89" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28374,7 +28374,7 @@
       </c>
       <c r="BP91" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="R92" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="S92" s="4" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="BP92" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29058,7 +29058,7 @@
       </c>
       <c r="BP93" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="BP94" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="BP95" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="BP96" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -30426,7 +30426,7 @@
       </c>
       <c r="BP97" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -31794,7 +31794,7 @@
       </c>
       <c r="BP101" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32136,7 +32136,7 @@
       </c>
       <c r="BP102" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="BP103" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -32820,7 +32820,7 @@
       </c>
       <c r="BP104" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -33504,7 +33504,7 @@
       </c>
       <c r="BP106" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Arm Cortex-M0+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -33846,7 +33846,7 @@
       </c>
       <c r="BP107" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -34910,9 +34910,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -35225,9 +35225,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35252,9 +35252,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -35567,9 +35567,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -35936,9 +35936,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -36251,9 +36251,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36278,9 +36278,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -36593,9 +36593,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36620,9 +36620,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -36935,9 +36935,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36962,9 +36962,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -37277,9 +37277,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37646,9 +37646,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -37961,9 +37961,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37988,9 +37988,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -38303,9 +38303,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38330,9 +38330,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -38645,9 +38645,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39014,9 +39014,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -39329,9 +39329,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39698,9 +39698,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -39923,14 +39923,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ27" s="6" t="inlineStr">
@@ -40013,9 +40013,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40040,9 +40040,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -40265,14 +40265,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ28" s="6" t="inlineStr">
@@ -40355,9 +40355,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40382,9 +40382,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -40607,14 +40607,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ29" s="6" t="inlineStr">
@@ -40697,9 +40697,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40724,9 +40724,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -40949,14 +40949,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ30" s="6" t="inlineStr">
@@ -41039,9 +41039,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41066,9 +41066,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -41291,14 +41291,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ31" s="6" t="inlineStr">
@@ -41381,9 +41381,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41408,9 +41408,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -41633,14 +41633,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ32" s="6" t="inlineStr">
@@ -41723,9 +41723,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41750,9 +41750,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -41975,14 +41975,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ33" s="6" t="inlineStr">
@@ -42065,9 +42065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42434,9 +42434,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -42659,14 +42659,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ35" s="6" t="inlineStr">
@@ -42749,9 +42749,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -42776,9 +42776,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -43001,14 +43001,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ36" s="6" t="inlineStr">
@@ -43091,9 +43091,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43118,9 +43118,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -43343,14 +43343,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ37" s="6" t="inlineStr">
@@ -43433,9 +43433,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43460,9 +43460,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -43685,14 +43685,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ38" s="6" t="inlineStr">
@@ -43775,9 +43775,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43802,9 +43802,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -44027,14 +44027,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ39" s="6" t="inlineStr">
@@ -44117,9 +44117,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44144,9 +44144,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -44369,14 +44369,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ40" s="6" t="inlineStr">
@@ -44459,9 +44459,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44486,9 +44486,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -44711,14 +44711,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ41" s="6" t="inlineStr">
@@ -44801,9 +44801,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45170,9 +45170,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -45395,14 +45395,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ43" s="8" t="inlineStr">
@@ -45485,9 +45485,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45512,9 +45512,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -45737,14 +45737,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ44" s="8" t="inlineStr">
@@ -45827,9 +45827,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46196,9 +46196,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -46421,14 +46421,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ46" s="8" t="inlineStr">
@@ -46511,9 +46511,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46538,9 +46538,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -46763,14 +46763,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ47" s="8" t="inlineStr">
@@ -46853,9 +46853,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46880,9 +46880,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -47105,14 +47105,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX48" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ48" s="8" t="inlineStr">
@@ -47195,9 +47195,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47222,9 +47222,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -47447,14 +47447,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX49" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ49" s="8" t="inlineStr">
@@ -47537,9 +47537,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47564,9 +47564,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -47789,14 +47789,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX50" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ50" s="8" t="inlineStr">
@@ -47879,9 +47879,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48248,9 +48248,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -48473,14 +48473,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX52" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY52" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ52" s="8" t="inlineStr">
@@ -48563,9 +48563,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48590,9 +48590,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -48815,14 +48815,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX53" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY53" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ53" s="8" t="inlineStr">
@@ -48905,9 +48905,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48932,9 +48932,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -49157,14 +49157,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ54" s="8" t="inlineStr">
@@ -49247,9 +49247,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49274,9 +49274,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -49499,14 +49499,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX55" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY55" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ55" s="8" t="inlineStr">
@@ -49589,9 +49589,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49616,9 +49616,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -49841,14 +49841,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ56" s="8" t="inlineStr">
@@ -49931,9 +49931,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49958,9 +49958,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -50023,14 +50023,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
@@ -50183,14 +50183,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY57" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY57" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ57" s="8" t="inlineStr">
@@ -50273,9 +50273,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50300,9 +50300,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -50365,14 +50365,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
@@ -50525,14 +50525,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY58" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY58" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ58" s="8" t="inlineStr">
@@ -50615,9 +50615,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50642,9 +50642,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -50707,14 +50707,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T59" s="6" t="inlineStr">
@@ -50867,14 +50867,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY59" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY59" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ59" s="8" t="inlineStr">
@@ -50957,9 +50957,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50984,9 +50984,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -51049,14 +51049,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
@@ -51209,14 +51209,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ60" s="8" t="inlineStr">
@@ -51299,9 +51299,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51326,9 +51326,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -51391,14 +51391,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -51551,14 +51551,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ61" s="8" t="inlineStr">
@@ -51641,9 +51641,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51668,9 +51668,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -51733,14 +51733,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -51893,14 +51893,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ62" s="8" t="inlineStr">
@@ -51983,9 +51983,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52352,9 +52352,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -52417,14 +52417,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
@@ -52577,14 +52577,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ64" s="8" t="inlineStr">
@@ -52667,9 +52667,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52694,9 +52694,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -52759,14 +52759,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -52919,14 +52919,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ65" s="8" t="inlineStr">
@@ -53009,9 +53009,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53036,9 +53036,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -53101,14 +53101,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T66" s="6" t="inlineStr">
@@ -53261,14 +53261,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY66" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY66" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ66" s="8" t="inlineStr">
@@ -53351,9 +53351,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53378,9 +53378,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -53443,14 +53443,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -53603,14 +53603,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ67" s="8" t="inlineStr">
@@ -53693,9 +53693,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53720,9 +53720,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -53785,14 +53785,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -53945,14 +53945,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ68" s="8" t="inlineStr">
@@ -54035,9 +54035,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54062,9 +54062,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -54127,14 +54127,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
@@ -54287,14 +54287,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ69" s="8" t="inlineStr">
@@ -54377,9 +54377,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54404,9 +54404,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -54469,14 +54469,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
@@ -54629,14 +54629,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ70" s="8" t="inlineStr">
@@ -54719,9 +54719,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54746,9 +54746,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -54811,14 +54811,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -54971,14 +54971,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ71" s="8" t="inlineStr">
@@ -55061,9 +55061,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55088,9 +55088,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -55153,14 +55153,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -55313,14 +55313,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ72" s="8" t="inlineStr">
@@ -55403,9 +55403,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55430,9 +55430,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -55495,14 +55495,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T73" s="6" t="inlineStr">
@@ -55655,14 +55655,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY73" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY73" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ73" s="8" t="inlineStr">
@@ -55745,9 +55745,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55772,9 +55772,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -55837,14 +55837,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -55997,14 +55997,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AX74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ74" s="8" t="inlineStr">
@@ -56087,9 +56087,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56798,9 +56798,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -57023,14 +57023,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX77" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY77" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ77" s="6" t="inlineStr">
@@ -57113,9 +57113,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57140,9 +57140,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -57365,14 +57365,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX78" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ78" s="6" t="inlineStr">
@@ -57455,9 +57455,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -57482,9 +57482,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -57707,14 +57707,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX79" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ79" s="6" t="inlineStr">
@@ -57797,9 +57797,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -59192,9 +59192,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -59417,14 +59417,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ84" s="6" t="inlineStr">
@@ -59507,9 +59507,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -59871,14 +59871,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -59941,14 +59941,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R86" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S86" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T86" s="6" t="inlineStr">
@@ -59996,9 +59996,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD86" s="6" t="inlineStr">
@@ -60041,9 +60041,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM86" s="6" t="inlineStr">
@@ -60101,14 +60101,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ86" s="6" t="inlineStr">
@@ -60191,9 +60191,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -60213,14 +60213,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -60283,14 +60283,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R87" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T87" s="6" t="inlineStr">
@@ -60338,9 +60338,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD87" s="6" t="inlineStr">
@@ -60383,9 +60383,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM87" s="6" t="inlineStr">
@@ -60443,14 +60443,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ87" s="6" t="inlineStr">
@@ -60533,9 +60533,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -60555,14 +60555,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -60625,14 +60625,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R88" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S88" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T88" s="6" t="inlineStr">
@@ -60680,9 +60680,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD88" s="6" t="inlineStr">
@@ -60725,9 +60725,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM88" s="6" t="inlineStr">
@@ -60785,14 +60785,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX88" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ88" s="6" t="inlineStr">
@@ -60875,9 +60875,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP88" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -60897,14 +60897,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -60967,14 +60967,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R89" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S89" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T89" s="6" t="inlineStr">
@@ -61022,9 +61022,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD89" s="6" t="inlineStr">
@@ -61067,9 +61067,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM89" s="6" t="inlineStr">
@@ -61127,14 +61127,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX89" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ89" s="6" t="inlineStr">
@@ -61217,9 +61217,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -61581,14 +61581,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -61651,14 +61651,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R91" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T91" s="6" t="inlineStr">
@@ -61706,9 +61706,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD91" s="6" t="inlineStr">
@@ -61751,9 +61751,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM91" s="6" t="inlineStr">
@@ -61811,14 +61811,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX91" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY91" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ91" s="6" t="inlineStr">
@@ -61901,9 +61901,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP91" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -61923,14 +61923,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -61993,14 +61993,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R92" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S92" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T92" s="6" t="inlineStr">
@@ -62048,9 +62048,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD92" s="6" t="inlineStr">
@@ -62093,9 +62093,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM92" s="6" t="inlineStr">
@@ -62153,14 +62153,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ92" s="6" t="inlineStr">
@@ -62243,9 +62243,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62265,14 +62265,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -62335,14 +62335,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R93" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S93" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T93" s="6" t="inlineStr">
@@ -62390,9 +62390,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD93" s="6" t="inlineStr">
@@ -62435,9 +62435,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM93" s="6" t="inlineStr">
@@ -62495,14 +62495,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX93" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ93" s="6" t="inlineStr">
@@ -62585,9 +62585,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP93" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62607,14 +62607,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -62677,14 +62677,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R94" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S94" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T94" s="6" t="inlineStr">
@@ -62732,9 +62732,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD94" s="6" t="inlineStr">
@@ -62777,9 +62777,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM94" s="6" t="inlineStr">
@@ -62837,14 +62837,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX94" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ94" s="6" t="inlineStr">
@@ -62927,9 +62927,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP94" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -62949,14 +62949,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -63019,14 +63019,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R95" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S95" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T95" s="6" t="inlineStr">
@@ -63074,9 +63074,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD95" s="8" t="inlineStr">
@@ -63119,9 +63119,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM95" s="6" t="inlineStr">
@@ -63179,14 +63179,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX95" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY95" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ95" s="6" t="inlineStr">
@@ -63269,9 +63269,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP95" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -63291,14 +63291,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -63361,14 +63361,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R96" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S96" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T96" s="6" t="inlineStr">
@@ -63416,9 +63416,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD96" s="8" t="inlineStr">
@@ -63461,9 +63461,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM96" s="6" t="inlineStr">
@@ -63521,14 +63521,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX96" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY96" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ96" s="6" t="inlineStr">
@@ -63611,9 +63611,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP96" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -63633,14 +63633,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -63703,14 +63703,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R97" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S97" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T97" s="6" t="inlineStr">
@@ -63758,9 +63758,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD97" s="6" t="inlineStr">
@@ -63803,9 +63803,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM97" s="6" t="inlineStr">
@@ -63863,14 +63863,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX97" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ97" s="6" t="inlineStr">
@@ -63953,9 +63953,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP97" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -65321,9 +65321,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP101" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -65663,9 +65663,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP102" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -65925,9 +65925,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AZ103" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AZ103" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA103" s="6" t="inlineStr">
@@ -66005,9 +66005,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP103" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -66347,9 +66347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP104" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP104" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -67031,9 +67031,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP106" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -67058,9 +67058,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -67373,9 +67373,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP107" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -67394,7 +67394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67450,7 +67450,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -67472,7 +67472,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -67494,7 +67494,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32WLE4C8</t>
+          <t>STM32WLE5C8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -67516,7 +67516,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32WLE5JB</t>
+          <t>STM32WBA50KG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -67531,19 +67531,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32WL54JC</t>
+          <t>STM32WBA52CE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -67553,19 +67553,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32WL54JC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -67575,19 +67575,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32WLE5CC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -67597,14 +67597,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32WLE5JC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -67619,19 +67619,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32WL55JC</t>
+          <t>STM32WBA62CI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -67641,14 +67641,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32WL55JC</t>
+          <t>STM32WBA25CE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -67663,14 +67663,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WB1MMC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -67685,19 +67685,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WB5MMG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -67707,14 +67707,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32WLE5J8</t>
+          <t>STM32WB10CC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -67729,14 +67729,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32WLE4J8</t>
+          <t>STM32WB50CG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -67751,14 +67751,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32WLE4JB</t>
+          <t>STM32WB15CC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -67773,19 +67773,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32WLE4CB</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -67795,14 +67795,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32WLE4CC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -67817,19 +67817,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32WLE4JC</t>
+          <t>STM32WB05KZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -67838,2734 +67838,6 @@
         </is>
       </c>
       <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WLE5CB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WLE5C8</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WBA52KE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WBA55UE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WBA50KG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 25. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WBA52KG</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32WBA54KG</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32WBA52CG</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32WBA55UG</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32WBA55CE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32WBA52CE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32WBA54KE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32WBA54CE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32WBA55HG</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32WBA54CG</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32WBA55CG</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 31. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32WBA62PI</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32WBA65CI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32WBA65MI</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32WBA62MI</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32WBA65PI</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32WBA64CG</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32WBA62CI</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32WBA65CG</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32WBA64CI</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32WBA62MG</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32WBA65PG</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32WBA63CG</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32WBA62PG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32WBA62CG</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32WBA65RI</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32WBA65RG</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32WBA63CI</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 17. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32WBA65MG</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) max</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 30. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.75 (2.75)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32WBA25CE</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32WBA23KE</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32WBA25HE</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32WBA23CE</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32WB1MMC</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32WB5MMG</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M0+, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32WB10CC</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32WB50CG</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32WB30CE</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 20. General operating conditions: V_DD min reads '2.0(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32WB15CC</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32WB55RC</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32WB55RC</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32WB05KZ</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32WB05TZ</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
         <is>
           <t>Table 15. Peripheral current consumption at V = 3.3 V, system clock (CLK_SYS), SMPS on</t>
         </is>

--- a/product_selector_out/STM32 wireless MCUs.xlsx
+++ b/product_selector_out/STM32 wireless MCUs.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BQ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.953125" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -919,6 +920,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1017,6 +1023,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1356,6 +1363,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
         </is>
       </c>
@@ -1701,6 +1713,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2043,6 +2060,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2382,6 +2404,11 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
@@ -2727,6 +2754,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3069,6 +3101,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3411,6 +3448,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3753,6 +3795,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4092,6 +4139,11 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
@@ -4437,6 +4489,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4779,6 +4836,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5121,6 +5183,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5460,6 +5527,11 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
         </is>
       </c>
@@ -5805,6 +5877,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6144,6 +6221,11 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl5moc.pdf</t>
         </is>
       </c>
@@ -6489,6 +6571,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -6831,6 +6918,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -7173,6 +7265,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -7515,6 +7612,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -7857,6 +7959,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -8199,6 +8306,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -8541,6 +8653,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -8880,6 +8997,11 @@
       </c>
       <c r="BP34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
@@ -9225,6 +9347,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -9567,6 +9694,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -9909,6 +10041,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -10251,6 +10388,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -10593,6 +10735,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -10935,6 +11082,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -11277,6 +11429,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -11616,6 +11773,11 @@
       </c>
       <c r="BP42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
@@ -11961,6 +12123,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -12303,6 +12470,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -12642,6 +12814,11 @@
       </c>
       <c r="BP45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba50kg.pdf</t>
         </is>
       </c>
@@ -12987,6 +13164,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -13329,6 +13511,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ47" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -13671,6 +13858,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ48" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -14013,6 +14205,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ49" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -14355,6 +14552,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ50" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -14694,6 +14896,11 @@
       </c>
       <c r="BP51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba52ce.pdf</t>
         </is>
       </c>
@@ -15039,6 +15246,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ52" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -15381,6 +15593,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ53" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -15723,6 +15940,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ54" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -16065,6 +16287,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ55" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -16407,6 +16634,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ56" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -16749,6 +16981,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ57" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -17091,6 +17328,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -17433,6 +17675,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ59" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -17775,6 +18022,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -18117,6 +18369,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -18459,6 +18716,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ62" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -18798,6 +19060,11 @@
       </c>
       <c r="BP63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba62ci.pdf</t>
         </is>
       </c>
@@ -19143,6 +19410,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ64" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -19485,6 +19757,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ65" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -19827,6 +20104,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ66" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -20169,6 +20451,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -20511,6 +20798,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -20853,6 +21145,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ69" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -21195,6 +21492,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -21537,6 +21839,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ71" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -21879,6 +22186,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -22221,6 +22533,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ73" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -22563,6 +22880,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ74" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -22902,6 +23224,11 @@
       </c>
       <c r="BP75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba5mmg.pdf</t>
         </is>
       </c>
@@ -23244,6 +23571,11 @@
       </c>
       <c r="BP76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
@@ -23589,6 +23921,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -23931,6 +24268,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -24273,6 +24615,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -24612,6 +24959,11 @@
       </c>
       <c r="BP80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb1mmc.pdf</t>
         </is>
       </c>
@@ -24954,6 +25306,11 @@
       </c>
       <c r="BP81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb5mmg.pdf</t>
         </is>
       </c>
@@ -25296,6 +25653,11 @@
       </c>
       <c r="BP82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb10cc.pdf</t>
         </is>
       </c>
@@ -25638,6 +26000,11 @@
       </c>
       <c r="BP83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb50cg.pdf</t>
         </is>
       </c>
@@ -25983,6 +26350,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -26322,6 +26694,11 @@
       </c>
       <c r="BP85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb15cc.pdf</t>
         </is>
       </c>
@@ -26667,6 +27044,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -27009,6 +27391,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ87" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -27351,6 +27738,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -27693,6 +28085,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ89" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -28032,6 +28429,11 @@
       </c>
       <c r="BP90" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BQ90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
@@ -28377,6 +28779,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -28719,6 +29126,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -29061,6 +29473,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ93" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -29403,6 +29820,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ94" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -29745,6 +30167,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -30087,6 +30514,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ96" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -30429,6 +30861,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ97" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -30768,6 +31205,11 @@
       </c>
       <c r="BP98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb06cc.pdf</t>
         </is>
       </c>
@@ -31110,6 +31552,11 @@
       </c>
       <c r="BP99" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ99" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb09ke.pdf</t>
         </is>
       </c>
@@ -31452,6 +31899,11 @@
       </c>
       <c r="BP100" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ100" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb05kz.pdf</t>
         </is>
       </c>
@@ -31797,6 +32249,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ101" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -32139,6 +32596,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ102" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -32481,6 +32943,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ103" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -32823,6 +33290,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -33162,6 +33634,11 @@
       </c>
       <c r="BP105" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ105" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb05kn.pdf</t>
         </is>
       </c>
@@ -33507,6 +33984,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ106" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -33849,9 +34331,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ107" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -33874,14 +34361,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -33899,6 +34385,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -33911,6 +34398,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -34029,7 +34517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BQ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34100,6 +34588,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34448,6 +34937,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -34546,6 +35040,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -34883,7 +35378,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35230,6 +35730,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -35572,6 +36077,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -35909,7 +36419,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36256,6 +36771,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -36598,6 +37118,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -36940,6 +37465,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -37282,6 +37812,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -37619,7 +38154,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37966,6 +38506,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -38308,6 +38853,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -38650,6 +39200,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -38987,7 +39542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39334,6 +39894,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -39671,7 +40236,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
+      <c r="BP26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40018,6 +40588,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -40360,6 +40935,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -40702,6 +41282,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -41044,6 +41629,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -41386,6 +41976,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -41728,6 +42323,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -42070,6 +42670,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -42407,7 +43012,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP34" s="6" t="inlineStr">
+      <c r="BP34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42754,6 +43364,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -43096,6 +43711,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -43438,6 +44058,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -43780,6 +44405,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -44122,6 +44752,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -44464,6 +45099,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -44806,6 +45446,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -45143,7 +45788,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP42" s="6" t="inlineStr">
+      <c r="BP42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45490,6 +46140,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -45832,6 +46487,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -46169,7 +46829,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP45" s="6" t="inlineStr">
+      <c r="BP45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46516,6 +47181,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -46858,6 +47528,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -47200,6 +47875,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -47542,6 +48222,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -47884,6 +48569,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -48221,7 +48911,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP51" s="6" t="inlineStr">
+      <c r="BP51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48568,6 +49263,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -48910,6 +49610,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -49252,6 +49957,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -49594,6 +50304,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -49936,6 +50651,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -50278,6 +50998,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -50620,6 +51345,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -50962,6 +51692,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -51304,6 +52039,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -51646,6 +52386,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -51988,6 +52733,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -52325,7 +53075,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP63" s="6" t="inlineStr">
+      <c r="BP63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52672,6 +53427,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -53014,6 +53774,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -53356,6 +54121,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -53698,6 +54468,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -54040,6 +54815,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -54382,6 +55162,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -54724,6 +55509,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -55066,6 +55856,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -55408,6 +56203,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -55750,6 +56550,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -56092,6 +56897,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -56429,7 +57239,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP75" s="6" t="inlineStr">
+      <c r="BP75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56771,7 +57586,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP76" s="6" t="inlineStr">
+      <c r="BP76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57118,6 +57938,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -57460,6 +58285,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -57802,6 +58632,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -58139,7 +58974,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP80" s="6" t="inlineStr">
+      <c r="BP80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58481,7 +59321,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP81" s="6" t="inlineStr">
+      <c r="BP81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58823,7 +59668,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP82" s="6" t="inlineStr">
+      <c r="BP82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59165,7 +60015,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP83" s="6" t="inlineStr">
+      <c r="BP83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59512,6 +60367,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -59849,7 +60709,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP85" s="6" t="inlineStr">
+      <c r="BP85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60196,6 +61061,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -60538,6 +61408,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -60880,6 +61755,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -61222,6 +62102,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -61559,7 +62444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP90" s="6" t="inlineStr">
+      <c r="BP90" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BQ90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61906,6 +62796,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -62248,6 +63143,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -62590,6 +63490,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -62932,6 +63837,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -63274,6 +64184,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -63616,6 +64531,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -63958,6 +64878,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -64295,7 +65220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP98" s="6" t="inlineStr">
+      <c r="BP98" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64637,7 +65567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP99" s="6" t="inlineStr">
+      <c r="BP99" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ99" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -64979,7 +65914,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP100" s="6" t="inlineStr">
+      <c r="BP100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ100" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -65326,6 +66266,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -65668,6 +66613,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -66010,6 +66960,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -66352,6 +67307,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ104" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -66689,7 +67649,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP105" s="6" t="inlineStr">
+      <c r="BP105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ105" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -67036,6 +68001,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -67378,11 +68348,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ107" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
